--- a/public/modele-blocs-types.xlsx
+++ b/public/modele-blocs-types.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
   <si>
     <t/>
   </si>
@@ -24,12 +24,24 @@
     <t>A quoi sert ce fichier</t>
   </si>
   <si>
-    <t>Il regroupe, pour chaque famille de coversheet, quelles exigences vont ensemble et la redaction qui leur correspond.</t>
+    <t>Il regroupe, pour chaque document de certification, quelles exigences vont ensemble et la redaction qui leur correspond.</t>
   </si>
   <si>
     <t>L'application le lit pour restituer la redaction deja ecrite au lieu de vous la faire reecrire a chaque standard.</t>
   </si>
   <si>
+    <t>La regle de la ligne</t>
+  </si>
+  <si>
+    <t>Une ligne = une exigence, ou un groupe d'exigences, pour UN SEUL document de certification.</t>
+  </si>
+  <si>
+    <t>Une exigence utilisee a la fois pour la SSA et pour le SyDMP occupe donc deux lignes distinctes :</t>
+  </si>
+  <si>
+    <t>les deux documents n'en disent pas la meme chose, ce sont deux justifications differentes.</t>
+  </si>
+  <si>
     <t>Ou le ranger</t>
   </si>
   <si>
@@ -45,10 +57,13 @@
     <t>Une ligne par bloc de justification. Remplissez la feuille "Blocs types".</t>
   </si>
   <si>
-    <t>Famille de coversheet</t>
-  </si>
-  <si>
-    <t>La famille du document de certification : SyDMP, SSA, VVS, SyDAS... C'est elle qui regroupe les blocs.</t>
+    <t>Document de certification</t>
+  </si>
+  <si>
+    <t>Le document que la coversheet accompagne : SyDMP, SSA, VVS, SyDAS... C'est lui qui regroupe les blocs.</t>
+  </si>
+  <si>
+    <t>L'application affiche cette liste au moment de preparer une coversheet : on choisit le document, puis ses exigences.</t>
   </si>
   <si>
     <t>Exigences</t>
@@ -119,17 +134,21 @@
     <t>SSA</t>
   </si>
   <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The enclosed safety assessment demonstrates in §x.x that the failure
+conditions associated with this requirement are adequately classified.</t>
+  </si>
+  <si>
+    <t>CVS-SSA fictive issue 4</t>
+  </si>
+  <si>
     <t>CS 25.671(c)(1) ; CS 25.1309(b)</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t xml:space="preserve">Combinations of failures have been classified in §x.x, and adequate failure
 probabilities are demonstrated in §x.x.</t>
-  </si>
-  <si>
-    <t>CVS-SSA fictive issue 4</t>
   </si>
 </sst>
 </file>
@@ -534,7 +553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -626,23 +645,23 @@
         <v>0</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="12" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -650,31 +669,31 @@
         <v>0</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>10</v>
+      <c r="A15" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>14</v>
+      <c r="B17" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -682,23 +701,23 @@
         <v>0</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>16</v>
+      <c r="A19" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -706,15 +725,15 @@
         <v>0</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -722,23 +741,71 @@
         <v>0</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2" t="s">
+      <c r="B26" s="2" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -752,7 +819,7 @@
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="90" customWidth="1"/>
@@ -761,19 +828,19 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -784,10 +851,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="46" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="90" customWidth="1"/>
@@ -796,70 +863,87 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/public/modele-blocs-types.xlsx
+++ b/public/modele-blocs-types.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="49">
   <si>
     <t/>
   </si>
@@ -93,6 +93,24 @@
     <t>L'application compte ces reperes et vous rappelle combien il en reste ; elle ne cherche jamais a les deviner.</t>
   </si>
   <si>
+    <t>Indication de recherche : ajoutez entre crochets, colle au repere, l'endroit ou l'information se</t>
+  </si>
+  <si>
+    <t>trouvait a l'edition precedente du document. Exemple : §x.x[5.4] ou §x.x[ch. 9].</t>
+  </si>
+  <si>
+    <t>L'application l'affiche en grise dans le champ de saisie : elle guide la recherche, elle ne la remplace pas.</t>
+  </si>
+  <si>
+    <t>Elle ne sort JAMAIS dans la coversheet produite : elle vient d'une edition anterieure et n'a pas ete verifiee.</t>
+  </si>
+  <si>
+    <t>Collez-la au repere plutot que dans une colonne a part : une liste en face du texte se decale</t>
+  </si>
+  <si>
+    <t>des qu'un repere est insere au milieu, et designe alors le mauvais paragraphe.</t>
+  </si>
+  <si>
     <t>Coversheet source</t>
   </si>
   <si>
@@ -115,9 +133,9 @@
   </si>
   <si>
     <t xml:space="preserve">The enclosed SyDMP is the master plan describing the development assurance
-activities to be performed for the change requests listed in §x.x.
-The SyDMP references in §x.x the other plans describing the activities to be
-performed, and provides in §x.x the list of applicable rules.</t>
+activities to be performed for the change requests listed in §x.x[2.1].
+The SyDMP references in §x.x[5.4] the other plans describing the activities to be
+performed, and provides in §x.x[9] the list of applicable rules.</t>
   </si>
   <si>
     <t>CVS-SYDMP fictive issue 1</t>
@@ -126,7 +144,7 @@
     <t>CS 25.671(a)</t>
   </si>
   <si>
-    <t xml:space="preserve">The enclosed SyDMP describes in §x.x the development assurance activities
+    <t xml:space="preserve">The enclosed SyDMP describes in §x.x[5.4] the development assurance activities
 applicable to this requirement, and justifies in §x.x the deviations to the
 applicable processes.</t>
   </si>
@@ -137,7 +155,7 @@
     <t>3</t>
   </si>
   <si>
-    <t xml:space="preserve">The enclosed safety assessment demonstrates in §x.x that the failure
+    <t xml:space="preserve">The enclosed safety assessment demonstrates in §x.x[4.2] that the failure
 conditions associated with this requirement are adequately classified.</t>
   </si>
   <si>
@@ -553,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -777,11 +795,11 @@
       </c>
     </row>
     <row r="28" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>26</v>
+      <c r="A28" s="2" t="s">
+        <v>0</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -789,15 +807,15 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>0</v>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -805,7 +823,63 @@
         <v>0</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -840,7 +914,7 @@
         <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -875,75 +949,75 @@
         <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
